--- a/data/trans_bre/P38C-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,16</t>
+          <t>1,03; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,99</t>
+          <t>-0,84; 8,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 12,31</t>
+          <t>1,26; 11,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 9,63</t>
+          <t>-0,95; 10,44</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,7</t>
+          <t>-2,83; 7,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,03</t>
+          <t>-2,56; 7,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 9,22</t>
+          <t>-3,18; 8,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 8,5</t>
+          <t>-2,92; 8,51</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 8,13</t>
+          <t>-4,48; 7,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 71,77</t>
+          <t>3,02; 68,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 9,7</t>
+          <t>-5,09; 9,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 376,02</t>
+          <t>3,61; 310,58</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,54</t>
+          <t>-1,18; 5,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 15,09</t>
+          <t>5,35; 15,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,8</t>
+          <t>-1,46; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 19,14</t>
+          <t>6,39; 19,84</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 10,8</t>
+          <t>2,64; 11,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 11,55</t>
+          <t>-18,09; 12,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 13,96</t>
+          <t>3,17; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 14,88</t>
+          <t>-22,03; 15,52</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,44; 39,47</t>
+          <t>26,41; 39,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,47; 47,45</t>
+          <t>23,44; 46,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,22; 81,73</t>
+          <t>44,43; 83,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,77; 132,47</t>
+          <t>40,75; 128,32</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,74</t>
+          <t>4,17; 7,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 31,44</t>
+          <t>4,37; 27,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,65</t>
+          <t>4,98; 9,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 55,05</t>
+          <t>5,59; 47,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38C-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,82</t>
+          <t>1,36; 10,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,66</t>
+          <t>-1,4; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,89</t>
+          <t>1,51; 12,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,44</t>
+          <t>-1,52; 9,64</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 7,1</t>
+          <t>-3,03; 6,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,01</t>
+          <t>-2,11; 7,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 8,63</t>
+          <t>-3,3; 8,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,51</t>
+          <t>-2,34; 8,86</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36,68</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,69</t>
+          <t>-4,56; 7,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 68,97</t>
+          <t>-0,14; 10,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 9,05</t>
+          <t>-5,27; 9,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 310,58</t>
+          <t>-0,11; 12,51</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,04</t>
+          <t>-0,77; 5,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 15,64</t>
+          <t>3,72; 10,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 6,14</t>
+          <t>-0,89; 6,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 19,84</t>
+          <t>4,55; 13,91</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>13,22</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,07</t>
+          <t>2,87; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 12,08</t>
+          <t>8,46; 17,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,24</t>
+          <t>3,42; 14,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 15,52</t>
+          <t>10,57; 25,01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35,51</t>
+          <t>38,28</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,41; 39,6</t>
+          <t>26,67; 39,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 46,16</t>
+          <t>26,86; 47,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,43; 83,01</t>
+          <t>44,47; 80,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,75; 128,32</t>
+          <t>48,19; 142,5</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,58</t>
+          <t>4,11; 7,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 27,78</t>
+          <t>5,4; 9,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,39</t>
+          <t>4,97; 9,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 47,17</t>
+          <t>6,69; 12,44</t>
         </is>
       </c>
     </row>
